--- a/数值：战斗构想.xlsx
+++ b/数值：战斗构想.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\33010\Desktop\work\babel\Build-Our-Babel-Hust-2023-Software-Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46501D9F-AC8E-4A78-BF4B-B31CA00D5DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BDB094C-0F39-4A45-AC84-33FDC6E264CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3D02B95B-D615-48E3-99A6-4B1DE53F79A9}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="132">
   <si>
     <t>开局（应该不会再进行修改）</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -508,6 +508,10 @@
   </si>
   <si>
     <t>无法行动，而且更加扎实！</t>
+  </si>
+  <si>
+    <t>这部分有点匆忙了……没办法（）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1896,7 +1900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E23E1D7E-FD79-489D-BF5D-5A654F82CBF7}">
-  <dimension ref="A1:V144"/>
+  <dimension ref="A1:V146"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
@@ -4750,6 +4754,11 @@
         <v>130</v>
       </c>
     </row>
+    <row r="146" spans="1:1">
+      <c r="A146" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
